--- a/data/trans_orig/Q5408-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q5408-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11115</t>
+          <t>9838</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12091</t>
+          <t>12512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17167</t>
+          <t>18451</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>279967</t>
+          <t>281603</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>290701</t>
+          <t>290756</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>329489</t>
+          <t>329724</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>340064</t>
+          <t>340185</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>616215</t>
+          <t>614787</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>628947</t>
+          <t>628711</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1196</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11465</t>
+          <t>11644</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19898</t>
+          <t>20388</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16909</t>
+          <t>16844</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38170</t>
+          <t>39458</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>28349</t>
+          <t>28021</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>52774</t>
+          <t>54062</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>188873</t>
+          <t>188207</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>202097</t>
+          <t>201994</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>290816</t>
+          <t>289347</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>312895</t>
+          <t>313186</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>485533</t>
+          <t>483870</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>511203</t>
+          <t>511123</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12641</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14999</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25780</t>
+          <t>26246</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21485</t>
+          <t>22058</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46508</t>
+          <t>44987</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36346</t>
+          <t>34743</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63735</t>
+          <t>63138</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>474144</t>
+          <t>474315</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>490459</t>
+          <t>489966</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>624222</t>
+          <t>625202</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>650411</t>
+          <t>649307</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1107294</t>
+          <t>1108311</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1136691</t>
+          <t>1137175</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -2331,12 +2331,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9763</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>9839</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15370</t>
+          <t>15273</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14773</t>
+          <t>14167</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14790</t>
+          <t>14571</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>7826</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23036</t>
+          <t>22343</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>290210</t>
+          <t>290425</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>303698</t>
+          <t>303767</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>333923</t>
+          <t>334686</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>349018</t>
+          <t>349096</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>630507</t>
+          <t>632058</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>649573</t>
+          <t>649428</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16706</t>
+          <t>15252</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8639</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26123</t>
+          <t>26749</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13494</t>
+          <t>13057</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34727</t>
+          <t>34095</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11303</t>
+          <t>10877</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28581</t>
+          <t>29778</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28570</t>
+          <t>28761</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>52160</t>
+          <t>53812</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>46101</t>
+          <t>45174</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>76781</t>
+          <t>76571</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>212770</t>
+          <t>212075</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>233612</t>
+          <t>234027</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>319679</t>
+          <t>318690</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>347646</t>
+          <t>347145</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>539448</t>
+          <t>538131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>573535</t>
+          <t>575443</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>90,08%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19167</t>
+          <t>19239</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>11881</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30792</t>
+          <t>30071</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21054</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44466</t>
+          <t>43129</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16981</t>
+          <t>17218</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>38520</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33465</t>
+          <t>33164</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63580</t>
+          <t>60314</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56470</t>
+          <t>55928</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91430</t>
+          <t>91242</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>509512</t>
+          <t>509255</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>533224</t>
+          <t>532930</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>657950</t>
+          <t>661567</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>691615</t>
+          <t>694105</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1176887</t>
+          <t>1179295</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1218235</t>
+          <t>1218334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -4042,12 +4042,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9097</t>
+          <t>10012</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4057,12 +4057,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>896</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13052</t>
+          <t>13555</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>325233</t>
+          <t>324318</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>333303</t>
+          <t>333328</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>369913</t>
+          <t>369663</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>376870</t>
+          <t>376866</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>699040</t>
+          <t>698537</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>709189</t>
+          <t>709097</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>2450</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12012</t>
+          <t>11335</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23904</t>
+          <t>23489</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11036</t>
+          <t>10964</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29686</t>
+          <t>29605</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -4498,12 +4498,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12858</t>
+          <t>12850</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28696</t>
+          <t>27578</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21689</t>
+          <t>21480</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45785</t>
+          <t>47582</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>39533</t>
+          <t>38958</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>67339</t>
+          <t>67044</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>221510</t>
+          <t>222890</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>239547</t>
+          <t>239554</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>338270</t>
+          <t>338020</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>367117</t>
+          <t>367346</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>568623</t>
+          <t>568214</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>602394</t>
+          <t>601896</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,59%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2427</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11545</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24655</t>
+          <t>23731</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>11442</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30102</t>
+          <t>30054</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15626</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34446</t>
+          <t>34177</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24271</t>
+          <t>25011</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50007</t>
+          <t>50311</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45069</t>
+          <t>44853</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75287</t>
+          <t>74996</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>550407</t>
+          <t>551194</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>570953</t>
+          <t>571412</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>711792</t>
+          <t>713049</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>743047</t>
+          <t>742614</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1271483</t>
+          <t>1272896</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1308108</t>
+          <t>1308889</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5592,32 +5592,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2373</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>5882</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -5635,32 +5635,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8984</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5670,32 +5670,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>6634</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18052</t>
+          <t>16816</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5705,32 +5705,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>14390</t>
+          <t>15266</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6454</t>
+          <t>10258</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21656</t>
+          <t>22889</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -5748,32 +5748,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>362590</t>
+          <t>401347</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>357853</t>
+          <t>395912</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>365539</t>
+          <t>404232</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5783,32 +5783,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>596285</t>
+          <t>426139</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>587961</t>
+          <t>420130</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>603731</t>
+          <t>430431</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5818,32 +5818,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>958874</t>
+          <t>827487</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>951194</t>
+          <t>819656</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>968335</t>
+          <t>833098</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -5861,17 +5861,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5896,17 +5896,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>607380</t>
+          <t>438046</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>607380</t>
+          <t>438046</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>607380</t>
+          <t>438046</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>975545</t>
+          <t>845126</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>975545</t>
+          <t>845126</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>975545</t>
+          <t>845126</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5978,32 +5978,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9131</t>
+          <t>9676</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6013,32 +6013,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15114</t>
+          <t>16593</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10390</t>
+          <t>11404</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21683</t>
+          <t>23211</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>19179</t>
+          <t>21226</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>15179</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26329</t>
+          <t>29305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -6091,32 +6091,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15268</t>
+          <t>15841</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10425</t>
+          <t>10914</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22166</t>
+          <t>23150</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6126,32 +6126,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46299</t>
+          <t>49060</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37749</t>
+          <t>39153</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>56385</t>
+          <t>59682</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6161,32 +6161,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>61567</t>
+          <t>64901</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51939</t>
+          <t>54616</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>73167</t>
+          <t>78861</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -6204,32 +6204,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>262679</t>
+          <t>288838</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>255173</t>
+          <t>281006</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>268440</t>
+          <t>295148</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6239,32 +6239,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>364419</t>
+          <t>398956</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>353084</t>
+          <t>387253</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>374450</t>
+          <t>410812</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6274,32 +6274,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>627098</t>
+          <t>687794</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>614612</t>
+          <t>673817</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>638988</t>
+          <t>700529</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,52%</t>
         </is>
       </c>
     </row>
@@ -6317,17 +6317,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6352,17 +6352,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6387,17 +6387,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>707844</t>
+          <t>773920</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>707844</t>
+          <t>773920</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>707844</t>
+          <t>773920</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6434,17 +6434,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>5892</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2473</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10568</t>
+          <t>11669</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -6469,32 +6469,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16130</t>
+          <t>17707</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23940</t>
+          <t>26107</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6504,32 +6504,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>21459</t>
+          <t>23599</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13574</t>
+          <t>17302</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30493</t>
+          <t>32008</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -6547,32 +6547,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19580</t>
+          <t>20315</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28006</t>
+          <t>28647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6582,32 +6582,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>56378</t>
+          <t>59852</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29721</t>
+          <t>47981</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76099</t>
+          <t>71184</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6617,32 +6617,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>75958</t>
+          <t>80167</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49871</t>
+          <t>68259</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93261</t>
+          <t>94457</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -6660,32 +6660,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>625269</t>
+          <t>690184</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>616380</t>
+          <t>681014</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>631884</t>
+          <t>697588</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6695,32 +6695,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>960703</t>
+          <t>825096</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>936266</t>
+          <t>813081</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>995017</t>
+          <t>838237</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6730,32 +6730,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1585972</t>
+          <t>1515280</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1565004</t>
+          <t>1499223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1618603</t>
+          <t>1528316</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -6773,17 +6773,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6808,17 +6808,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1033211</t>
+          <t>902655</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1033211</t>
+          <t>902655</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1033211</t>
+          <t>902655</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1683389</t>
+          <t>1619046</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1683389</t>
+          <t>1619046</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1683389</t>
+          <t>1619046</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
